--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="490">
   <si>
     <t>Filename</t>
   </si>
@@ -808,694 +808,682 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9954,0.0007,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0129,0.0001,0.0000,0.9979</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9931,0.0021,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0053,0.0000,0.0000,0.9994</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0416,0.0001,0.0000,0.9947</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0094,0.0002,0.0001,0.9981</t>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.5109,0.0011,0.5942,0.0001</t>
+  </si>
+  <si>
+    <t>0.0191,0.0021,0.9745,0.0014</t>
+  </si>
+  <si>
+    <t>0.7982,0.0029,0.1774,0.0001</t>
+  </si>
+  <si>
+    <t>0.0056,0.0014,0.9921,0.0003</t>
+  </si>
+  <si>
+    <t>0.8232,0.0042,0.1552,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.9906,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9681,0.0022,0.0183,0.0002</t>
+  </si>
+  <si>
+    <t>0.6367,0.0003,0.5026,0.0001</t>
+  </si>
+  <si>
+    <t>0.0082,0.0002,0.9909,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0830,0.0002,0.9477,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8198,0.1725,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9044,0.0194,0.0307,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9926,0.3034,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9730,0.0003,0.0314,0.0003</t>
+  </si>
+  <si>
+    <t>0.6671,0.4112,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0017,0.9972,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.4785,0.7356,0.0130</t>
+  </si>
+  <si>
+    <t>0.0024,0.0002,0.9917,0.0035</t>
+  </si>
+  <si>
+    <t>0.0001,0.0072,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0218,0.0002,0.9736,0.0015</t>
+  </si>
+  <si>
+    <t>0.0017,0.0891,0.9883,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0049,0.9973,0.0010</t>
+  </si>
+  <si>
+    <t>0.0039,0.0134,0.0008,0.9905</t>
+  </si>
+  <si>
+    <t>0.0013,0.9979,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9982,0.0346,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0037,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.1306,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9956,0.0018,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,0.9999,0.0049</t>
+  </si>
+  <si>
+    <t>0.9981,0.0012,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0002,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9800,0.9759,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0103,0.0019,0.9800,0.0017</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.9971,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.8314,0.0006,0.2502,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0002,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9997,0.0033</t>
+  </si>
+  <si>
+    <t>0.0000,0.9951,0.9927,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9965,0.9851,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9738,0.5822,0.0003</t>
+  </si>
+  <si>
+    <t>0.0069,0.0000,0.1258,0.8986</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0015,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.4618,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.9962,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9718,0.9858,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9700,0.9772,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9904,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9855,0.9213,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0010,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0156,0.9622,0.0313,0.0010</t>
+  </si>
+  <si>
+    <t>0.0042,0.9924,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.4930,0.5475,0.0078,0.0003</t>
+  </si>
+  <si>
+    <t>0.0695,0.1436,0.6849,0.0030</t>
+  </si>
+  <si>
+    <t>0.2628,0.0004,0.7490,0.0019</t>
+  </si>
+  <si>
+    <t>0.8577,0.0021,0.0947,0.0011</t>
+  </si>
+  <si>
+    <t>0.0086,0.0027,0.9822,0.0012</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.0053,0.9972</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9886,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9970,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.6012,0.3863,0.0047,0.0007</t>
+  </si>
+  <si>
+    <t>0.9570,0.0272,0.0050,0.0009</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0005,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9948,0.9584,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9665,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0037,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.4141,0.0017,0.5391,0.0028</t>
+  </si>
+  <si>
+    <t>0.0038,0.0001,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.9445,0.0107,0.0089,0.0008</t>
+  </si>
+  <si>
+    <t>0.0127,0.0000,0.0000,0.9983</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0021,0.9998</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0024,0.9993</t>
+  </si>
+  <si>
+    <t>0.0000,0.9794,0.9974,0.0000</t>
+  </si>
+  <si>
+    <t>0.0082,0.9871,0.0016,0.0013</t>
+  </si>
+  <si>
+    <t>0.8962,0.0947,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9494,0.0002,0.0000,0.0454</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0422,0.9972,0.0005</t>
+  </si>
+  <si>
+    <t>0.9955,0.0001,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.9967,0.0000,0.0012,0.0011</t>
+  </si>
+  <si>
+    <t>0.2970,0.6797,0.0034,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9951,0.0008,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.3951,0.1283,0.0759,0.0008</t>
+  </si>
+  <si>
+    <t>0.9824,0.0089,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0002,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9694,0.0080,0.0094,0.0010</t>
+  </si>
+  <si>
+    <t>0.5256,0.2232,0.0935,0.0008</t>
+  </si>
+  <si>
+    <t>0.8890,0.0324,0.0495,0.0010</t>
+  </si>
+  <si>
+    <t>0.9953,0.0060,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0002,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9964,0.0010,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9579,0.0364,0.0033,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.0047,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9699,0.0156,0.0062,0.0025</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.1296,0.0015,0.8895,0.0009</t>
+  </si>
+  <si>
+    <t>0.0293,0.0003,0.9805,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.0008,0.9986,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0062,0.0018,0.9864,0.0015</t>
+  </si>
+  <si>
+    <t>0.6188,0.0012,0.4565,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0017,0.9940,0.0009</t>
+  </si>
+  <si>
+    <t>0.2158,0.0054,0.6935,0.0007</t>
+  </si>
+  <si>
+    <t>0.0015,0.0519,0.9908,0.0001</t>
+  </si>
+  <si>
+    <t>0.0085,0.0049,0.9866,0.0001</t>
+  </si>
+  <si>
+    <t>0.6291,0.0126,0.1962,0.0017</t>
+  </si>
+  <si>
+    <t>0.7145,0.0009,0.2792,0.0014</t>
+  </si>
+  <si>
+    <t>0.0007,0.9980,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9982,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.0298,0.9689,0.0022,0.0005</t>
+  </si>
+  <si>
+    <t>0.7071,0.4310,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.4214,0.6685,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9724,0.0070,0.0042,0.0001</t>
+  </si>
+  <si>
+    <t>0.9940,0.0002,0.0040,0.0000</t>
+  </si>
+  <si>
+    <t>0.9829,0.0017,0.0034,0.0005</t>
+  </si>
+  <si>
+    <t>0.9187,0.0012,0.0956,0.0000</t>
+  </si>
+  <si>
+    <t>0.0556,0.0003,0.9583,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0057,0.0039,0.9862,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.0228,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.0011,0.9960,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0019,0.9984,0.0003</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9926,0.0074,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9955,0.0030,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0017,0.9993,0.0008</t>
+  </si>
+  <si>
+    <t>0.0044,0.9589,0.0294,0.0037</t>
+  </si>
+  <si>
+    <t>0.8283,0.0001,0.1351,0.0044</t>
+  </si>
+  <si>
+    <t>0.0022,0.0000,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0067,0.9986,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.3318,0.9797,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0002,0.9973,0.0005</t>
+  </si>
+  <si>
+    <t>0.0037,0.0022,0.9927,0.0003</t>
+  </si>
+  <si>
+    <t>0.0071,0.0007,0.9878,0.0008</t>
+  </si>
+  <si>
+    <t>0.9885,0.0007,0.0047,0.0000</t>
+  </si>
+  <si>
+    <t>0.9076,0.0003,0.1259,0.0002</t>
+  </si>
+  <si>
+    <t>0.9952,0.0001,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0044,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0003,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9991,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0004,0.9969,0.0005</t>
-  </si>
-  <si>
-    <t>0.9387,0.0014,0.0533,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.9981,0.0002</t>
-  </si>
-  <si>
-    <t>0.9291,0.0017,0.0556,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.9935,0.0031,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9136,0.0003,0.1080,0.0002</t>
-  </si>
-  <si>
-    <t>0.9929,0.0000,0.0085,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0004,0.9947,0.0007</t>
-  </si>
-  <si>
-    <t>0.0030,0.0021,0.9913,0.0006</t>
-  </si>
-  <si>
-    <t>0.1189,0.0002,0.9372,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.2125,0.7458,0.0027,0.0012</t>
-  </si>
-  <si>
-    <t>0.5882,0.0496,0.1630,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.9953,0.0302,0.0003</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9386,0.0010,0.0649,0.0004</t>
-  </si>
-  <si>
-    <t>0.8058,0.2133,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.9988,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0117,0.3159,0.6141,0.0109</t>
-  </si>
-  <si>
-    <t>0.0024,0.0003,0.9930,0.0023</t>
-  </si>
-  <si>
-    <t>0.0019,0.0021,0.9949,0.0003</t>
-  </si>
-  <si>
-    <t>0.0026,0.0001,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.7127,0.9965,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0234,0.0019,0.9712,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.1114,0.0001,0.9920</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0058,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0016,0.9971,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0014,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0001,0.9971,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.0019,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.9969,0.0011,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9972,0.0003,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9999,0.0041</t>
-  </si>
-  <si>
-    <t>0.9983,0.0004,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0004,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9808,0.9933,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0195,0.9955,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9976,0.9928,0.0000</t>
-  </si>
-  <si>
-    <t>0.0032,0.9961,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9477,0.0003,0.0876,0.0001</t>
-  </si>
-  <si>
-    <t>0.9179,0.0008,0.1055,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9997,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9939,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9940,0.9442,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9717,0.9936,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0002,0.1389,0.9744</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0003,0.9997</t>
-  </si>
-  <si>
-    <t>0.0029,0.0001,0.0004,0.9979</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0002,0.9943,0.0809,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.9426,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9867,0.9928,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9932,0.9499,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9945,0.9907,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8484,0.9956,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0017,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9862,0.0227,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0063,0.0001,0.9958,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.0004,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.9933,0.0001,0.0050,0.0000</t>
-  </si>
-  <si>
-    <t>0.0447,0.0003,0.9735,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.9915,0.0051,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.9983,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0583,0.9447,0.0053,0.0002</t>
-  </si>
-  <si>
-    <t>0.9677,0.0045,0.0099,0.0014</t>
-  </si>
-  <si>
-    <t>0.1001,0.0092,0.8511,0.0010</t>
-  </si>
-  <si>
-    <t>0.7771,0.0128,0.1006,0.0014</t>
-  </si>
-  <si>
-    <t>0.0067,0.0018,0.9884,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.0030,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.9916,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.9954,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.8529,0.1392,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.9844,0.0088,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0002,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.8185,0.9962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9409,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8928,0.0069,0.0575,0.0030</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.9002,0.0063,0.0618,0.0004</t>
-  </si>
-  <si>
-    <t>0.0265,0.0000,0.0000,0.9966</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0002,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0426,0.9983</t>
-  </si>
-  <si>
-    <t>0.0000,0.9916,0.9932,0.0000</t>
-  </si>
-  <si>
-    <t>0.0355,0.9532,0.0008,0.0035</t>
-  </si>
-  <si>
-    <t>0.0102,0.9856,0.0039,0.0003</t>
-  </si>
-  <si>
-    <t>0.9982,0.0002,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.8928,0.0003,0.0001,0.1840</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0846,0.9981,0.0002</t>
-  </si>
-  <si>
-    <t>0.8889,0.0000,0.0071,0.0299</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.1772,0.7151,0.0232,0.0004</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0004,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.1133,0.1374,0.3361,0.0010</t>
-  </si>
-  <si>
-    <t>0.9892,0.0006,0.0053,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9952,0.0011,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0021,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8901,0.0772,0.0155,0.0007</t>
-  </si>
-  <si>
-    <t>0.2341,0.7681,0.0078,0.0005</t>
-  </si>
-  <si>
-    <t>0.8977,0.0623,0.0240,0.0017</t>
-  </si>
-  <si>
-    <t>0.9801,0.0224,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9965,0.0019,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9278,0.0655,0.0023,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.0052,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9886,0.0027,0.0044,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0578,0.9958,0.0006</t>
-  </si>
-  <si>
-    <t>0.0011,0.0002,0.9986,0.0003</t>
-  </si>
-  <si>
-    <t>0.0024,0.0032,0.9953,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0051,0.0012,0.9920,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0013,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0047,0.0019,0.9875,0.0013</t>
-  </si>
-  <si>
-    <t>0.4522,0.0160,0.3359,0.0003</t>
-  </si>
-  <si>
-    <t>0.0435,0.0444,0.8116,0.0001</t>
-  </si>
-  <si>
-    <t>0.0610,0.0044,0.9387,0.0001</t>
-  </si>
-  <si>
-    <t>0.8588,0.0056,0.0492,0.0040</t>
-  </si>
-  <si>
-    <t>0.0209,0.0021,0.9739,0.0006</t>
-  </si>
-  <si>
-    <t>0.0067,0.9911,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.0021,0.9954,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.0476,0.9543,0.0028,0.0004</t>
-  </si>
-  <si>
-    <t>0.8444,0.2659,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9747,0.0383,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9912,0.0006,0.0024,0.0000</t>
-  </si>
-  <si>
-    <t>0.9801,0.0006,0.0178,0.0000</t>
-  </si>
-  <si>
-    <t>0.9892,0.0002,0.0047,0.0003</t>
-  </si>
-  <si>
-    <t>0.0593,0.0026,0.9535,0.0001</t>
-  </si>
-  <si>
-    <t>0.5769,0.0013,0.4523,0.0002</t>
-  </si>
-  <si>
-    <t>0.0016,0.0001,0.9982,0.0003</t>
-  </si>
-  <si>
-    <t>0.0013,0.0055,0.9946,0.0021</t>
-  </si>
-  <si>
-    <t>0.0008,0.0023,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0085,0.0006,0.9920,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0184,0.9884,0.0004</t>
+    <t>0.9973,0.0020,0.0003,0.0001</t>
   </si>
   <si>
     <t>0.9994,0.0002,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9988,0.0004,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0006,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9544,0.0784,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0157,0.9987,0.0004</t>
-  </si>
-  <si>
-    <t>0.0031,0.5049,0.7350,0.0007</t>
-  </si>
-  <si>
-    <t>0.8610,0.0002,0.1518,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0008,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0112,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9995,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0012,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0063,0.0003,0.9904,0.0009</t>
-  </si>
-  <si>
-    <t>0.9963,0.0001,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.9187,0.0001,0.1237,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0001,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9948,0.0037,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9849,0.0178,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0025,0.0195,0.9881,0.0004</t>
-  </si>
-  <si>
-    <t>0.0041,0.0921,0.9256,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.4013,0.0001,0.2652,0.0260</t>
-  </si>
-  <si>
-    <t>0.6674,0.0011,0.3744,0.0004</t>
-  </si>
-  <si>
-    <t>0.0021,0.0000,0.9974,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0001,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.0004,0.0008,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.4851,0.0010,0.0001,0.6720</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.6065,0.0001,0.0009,0.5342</t>
+    <t>0.9995,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0275,0.0090,0.9398,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0013,0.9976,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0018,0.9979,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.8784,0.0001,0.0561,0.0066</t>
+  </si>
+  <si>
+    <t>0.0027,0.0002,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9968,0.0005</t>
+  </si>
+  <si>
+    <t>0.9971,0.0001,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.0018,0.0064,0.0000,0.9987</t>
+  </si>
+  <si>
+    <t>0.1005,0.0002,0.0002,0.9771</t>
+  </si>
+  <si>
+    <t>0.9958,0.0003,0.0005,0.0010</t>
   </si>
 </sst>
 </file>
@@ -1881,7 +1869,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1895,7 +1883,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1909,7 +1897,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1923,7 +1911,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1937,7 +1925,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1951,7 +1939,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1965,7 +1953,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1979,7 +1967,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1993,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2007,7 +1995,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2021,7 +2009,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2035,7 +2023,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2046,10 +2034,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2063,7 +2051,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2077,7 +2065,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2091,7 +2079,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2105,7 +2093,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2119,7 +2107,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2133,7 +2121,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2147,7 +2135,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2161,7 +2149,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2175,7 +2163,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2189,7 +2177,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2200,10 +2188,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2217,7 +2205,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2231,7 +2219,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2245,7 +2233,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2259,7 +2247,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2273,7 +2261,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2284,10 +2272,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2301,7 +2289,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2315,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2329,7 +2317,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2343,7 +2331,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2357,7 +2345,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2371,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2385,7 +2373,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2399,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2413,7 +2401,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2427,7 +2415,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2441,7 +2429,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2452,10 +2440,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2469,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2483,7 +2471,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2497,7 +2485,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2511,7 +2499,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2525,7 +2513,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2539,7 +2527,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2553,7 +2541,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2567,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2581,7 +2569,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2595,7 +2583,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2609,7 +2597,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2623,7 +2611,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2637,7 +2625,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2651,7 +2639,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2665,7 +2653,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2679,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2693,7 +2681,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2707,7 +2695,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2721,7 +2709,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2735,7 +2723,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2749,7 +2737,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2763,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2777,7 +2765,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2791,7 +2779,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>289</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2805,7 +2793,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2819,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>327</v>
+        <v>282</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2833,7 +2821,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2847,7 +2835,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2861,7 +2849,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2875,7 +2863,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2889,7 +2877,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2903,7 +2891,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2917,7 +2905,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2931,7 +2919,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2945,7 +2933,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2959,7 +2947,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2973,7 +2961,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2987,7 +2975,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3001,7 +2989,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3015,7 +3003,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3029,7 +3017,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3043,7 +3031,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3057,7 +3045,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3071,7 +3059,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3085,7 +3073,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3099,7 +3087,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>271</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3113,7 +3101,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3127,7 +3115,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3141,7 +3129,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3155,7 +3143,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3169,7 +3157,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3183,7 +3171,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3197,7 +3185,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3211,7 +3199,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>273</v>
+        <v>357</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3225,7 +3213,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>273</v>
+        <v>358</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3239,7 +3227,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>354</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3253,7 +3241,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>273</v>
+        <v>359</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3267,7 +3255,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>273</v>
+        <v>357</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3281,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3295,7 +3283,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3309,7 +3297,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3323,7 +3311,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3337,7 +3325,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3351,7 +3339,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3365,7 +3353,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3379,7 +3367,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3393,7 +3381,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>361</v>
+        <v>312</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3407,7 +3395,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3421,7 +3409,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3435,7 +3423,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>327</v>
+        <v>286</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3449,7 +3437,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>364</v>
+        <v>286</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3463,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3474,10 +3462,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3491,7 +3479,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3505,7 +3493,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3519,7 +3507,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3533,7 +3521,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3547,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3561,7 +3549,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>372</v>
+        <v>286</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3575,7 +3563,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3589,7 +3577,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3603,7 +3591,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3617,7 +3605,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3631,7 +3619,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3645,7 +3633,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3659,7 +3647,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3673,7 +3661,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3701,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>273</v>
+        <v>350</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3715,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>273</v>
+        <v>382</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3729,7 +3717,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3743,7 +3731,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>383</v>
+        <v>272</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3813,7 +3801,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>388</v>
+        <v>273</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3824,10 +3812,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3841,7 +3829,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3855,7 +3843,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3869,7 +3857,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3883,7 +3871,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>393</v>
+        <v>341</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3897,7 +3885,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3911,7 +3899,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3925,7 +3913,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3939,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3953,7 +3941,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3978,10 +3966,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3995,7 +3983,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4009,7 +3997,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4023,7 +4011,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4037,7 +4025,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4051,7 +4039,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4065,7 +4053,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4079,7 +4067,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4093,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4107,7 +4095,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4118,10 +4106,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D162" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4135,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4149,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4163,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4177,7 +4165,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>266</v>
+        <v>410</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4205,7 +4193,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>412</v>
+        <v>363</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4219,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4233,7 +4221,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4247,7 +4235,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4261,7 +4249,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4275,7 +4263,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4289,7 +4277,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4300,10 +4288,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4317,7 +4305,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4331,7 +4319,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4345,7 +4333,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4359,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4373,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4387,7 +4375,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4401,7 +4389,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4415,7 +4403,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4429,7 +4417,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4443,7 +4431,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4457,7 +4445,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4471,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4485,7 +4473,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>431</v>
+        <v>293</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4499,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>432</v>
+        <v>293</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4513,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4524,10 +4512,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4541,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4552,10 +4540,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4569,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4583,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4597,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4608,10 +4596,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4625,7 +4613,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4639,7 +4627,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4653,7 +4641,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4667,7 +4655,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4678,10 +4666,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4695,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4709,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4723,7 +4711,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4734,10 +4722,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4748,10 +4736,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4765,7 +4753,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4779,7 +4767,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4793,7 +4781,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4807,7 +4795,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4821,7 +4809,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4835,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>456</v>
+        <v>273</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4849,7 +4837,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4863,7 +4851,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4877,7 +4865,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4891,7 +4879,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4905,7 +4893,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4919,7 +4907,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>462</v>
+        <v>270</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4933,7 +4921,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>463</v>
+        <v>270</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4947,7 +4935,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4958,10 +4946,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4975,7 +4963,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4989,7 +4977,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5003,7 +4991,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5017,7 +5005,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5031,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>289</v>
+        <v>464</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5045,7 +5033,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5059,7 +5047,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>471</v>
+        <v>293</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5073,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5087,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5101,7 +5089,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5115,7 +5103,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5129,7 +5117,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5143,7 +5131,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5157,7 +5145,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5171,7 +5159,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5185,7 +5173,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5199,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>273</v>
+        <v>475</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5213,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5227,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5241,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5255,7 +5243,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5269,7 +5257,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>431</v>
+        <v>479</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5283,7 +5271,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5297,7 +5285,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5311,7 +5299,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5325,7 +5313,7 @@
         <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5336,10 +5324,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5353,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5367,7 +5355,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5381,7 +5369,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5395,7 +5383,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5409,7 +5397,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>492</v>
+        <v>341</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5423,7 +5411,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>492</v>
+        <v>341</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5434,10 +5422,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
